--- a/materials/05_見積単価表.xlsx
+++ b/materials/05_見積単価表.xlsx
@@ -455,7 +455,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1クラス最大20名</t>
+          <t>1クラス最大24名</t>
         </is>
       </c>
     </row>
@@ -577,11 +577,11 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>現場課題持ち込み型の演習設計を含む</t>
+          <t>業務課題持ち込み型の演習設計・架空データ作成を含む</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>受講前のスキル診断（Web）</t>
+          <t>受講前の生成AI活用度診断（Web）</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>効果測定フォローアップ</t>
+          <t>事後フォローアップ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>受講3か月後の成果発表会の企画・運営</t>
+          <t>研修1か月後のオンライン共有会（90分）の企画・運営</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>受講者の合計が50名以上</t>
+          <t>1クラスあたり2日以上の実施</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>教材費（P03）を10%割引</t>
+          <t>講師料（P01）を5%割引</t>
         </is>
       </c>
     </row>
@@ -745,27 +745,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>同一コースを3クラス以上実施</t>
+          <t>その他の値引き</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>講師料（P01）を5%割引</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>割引の併用</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1と2は併用可。その他の値引きは営業部長の承認が必要</t>
+          <t>営業部長の承認が必要</t>
         </is>
       </c>
     </row>
@@ -780,22 +765,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>見積試算（みなと精機 若手技術者向けDX基礎研修）</t>
+          <t>見積試算（みらい商事 法人営業向け生成AI活用研修）A案・B案</t>
         </is>
       </c>
     </row>
@@ -807,10 +792,14 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>値</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n"/>
+          <t>A案</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>B案</t>
+        </is>
+      </c>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
@@ -826,173 +815,203 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>クラス数</t>
+          <t>日数</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1クラスあたり日数</t>
+          <t>実施形式（集合／オンライン）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>実施形式（集合／オンライン）</t>
+          <t>会場（顧客会場／ELI会場）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>会場（顧客会場／ELI会場）</t>
+          <t>アシスタント講師（あり／なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>研修カスタマイズ（あり／なし）</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>コード</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>単価</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>小計</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>割引</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>金額</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>事後フォローアップ（あり／なし）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>講師料</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>コード</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>アシスタント講師料</t>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>単価</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A案 数量</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>A案 金額</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>B案 数量</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>B案 金額</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>教材費</t>
+          <t>講師料</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>研修カスタマイズ費</t>
+          <t>アシスタント講師料</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>事前アセスメント</t>
+          <t>教材費</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>効果測定フォローアップ</t>
+          <t>研修カスタマイズ費</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ELI会場使用料</t>
+          <t>事前アセスメント</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>事後フォローアップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ELI会場使用料</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>P08</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>オンライン配信運営費</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>割引</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t>合計（税別）</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>※ 演習10で、Copilot を使って前提条件の入力と数式の作成を行います。</t>
         </is>

--- a/materials/05_見積単価表.xlsx
+++ b/materials/05_見積単価表.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="単価表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="割引ルール" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="含まないもの" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="見積試算" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -146,14 +146,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="単価表" displayName="単価表" ref="A1:E9" headerRowCount="1">
-  <autoFilter ref="A1:E9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="単価表" displayName="単価表" ref="A1:E5" headerRowCount="1">
+  <autoFilter ref="A1:E5"/>
   <tableColumns count="5">
     <tableColumn id="1" name="コード"/>
     <tableColumn id="2" name="項目"/>
     <tableColumn id="3" name="単位"/>
-    <tableColumn id="4" name="単価（円・税別）"/>
-    <tableColumn id="5" name="備考"/>
+    <tableColumn id="4" name="単価（円・税抜）"/>
+    <tableColumn id="5" name="内容"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -448,14 +448,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,12 +476,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>単価（円・税別）</t>
+          <t>単価（円・税抜）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
@@ -493,20 +493,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>講師料</t>
+          <t>集合研修（2日間）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1クラス・1日</t>
+          <t>1クラス（20名まで）</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>250000</v>
+        <v>500000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1クラス最大24名</t>
+          <t>基本とセキュリティ＋Word・Excel・PowerPoint を使った営業演習。A案・B案共通</t>
         </is>
       </c>
     </row>
@@ -518,20 +518,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>アシスタント講師料</t>
+          <t>教材</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1クラス・1日</t>
+          <t>1名</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>80000</v>
+        <v>5000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>演習中心のコースで推奨</t>
+          <t>テキスト・演習ファイル一式</t>
         </is>
       </c>
     </row>
@@ -543,20 +543,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>教材費</t>
+          <t>事前診断</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1名・1日</t>
+          <t>1式</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5000</v>
+        <v>200000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>テキスト・演習ファイル一式</t>
+          <t>事前の簡易アンケートと重点整理（B案のみ）</t>
         </is>
       </c>
     </row>
@@ -568,12 +568,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>研修カスタマイズ費</t>
+          <t>受講後1か月の活用フォロー</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1プログラム</t>
+          <t>1式</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -581,107 +581,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>業務課題持ち込み型の演習設計・架空データ作成を含む</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>P05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>事前アセスメント</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1名</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>受講前の生成AI活用度診断（Web）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>事後フォローアップ</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1回</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>研修1か月後のオンライン共有会（90分）の企画・運営</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ELI会場使用料</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1クラス・1日</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>顧客会場で実施する場合は不要</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>P08</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>オンライン配信運営費</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1クラス・1日</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>オンライン実施の場合のみ</t>
+          <t>活用シート回収・整理、オンライン振り返り1回、担当者向け簡易報告（B案のみ）</t>
         </is>
       </c>
     </row>
@@ -699,12 +599,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -715,12 +614,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>条件</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>割引内容</t>
+          <t>見積に含まないもの</t>
         </is>
       </c>
     </row>
@@ -730,12 +624,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1クラスあたり2日以上の実施</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>講師料（P01）を5%割引</t>
+          <t>会場・端末・必要なライセンス（お客様で手配）</t>
         </is>
       </c>
     </row>
@@ -745,12 +634,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>その他の値引き</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>営業部長の承認が必要</t>
+          <t>無制限の個別相談</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>アプリ開発</t>
         </is>
       </c>
     </row>
@@ -765,11 +659,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -780,7 +674,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>見積試算（みらい商事 法人営業向け生成AI活用研修）A案・B案</t>
+          <t>概算見積（みらい商事 法人営業向け生成AI活用研修）A案・B案</t>
         </is>
       </c>
     </row>
@@ -815,203 +709,134 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>日数</t>
+          <t>クラス数</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>実施形式（集合／オンライン）</t>
+          <t>事前診断（あり／なし）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>会場（顧客会場／ELI会場）</t>
+          <t>活用フォロー（あり／なし）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>アシスタント講師（あり／なし）</t>
-        </is>
-      </c>
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>研修カスタマイズ（あり／なし）</t>
+          <t>コード</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>単価</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A案 数量</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>A案 金額</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>B案 数量</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>B案 金額</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>事後フォローアップ（あり／なし）</t>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>集合研修（2日間）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>教材</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>コード</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>単価</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>A案 数量</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>A案 金額</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>B案 数量</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>B案 金額</t>
+          <t>事前診断</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>講師料</t>
+          <t>受講後1か月の活用フォロー</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>アシスタント講師料</t>
+          <t>合計（税抜）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>教材費</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>研修カスタマイズ費</t>
+          <t>1名あたり</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
-        <is>
-          <t>P05</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>事前アセスメント</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>事後フォローアップ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>P07</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ELI会場使用料</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>P08</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>オンライン配信運営費</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>割引</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>合計（税別）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
         <is>
           <t>※ 演習10で、Copilot を使って前提条件の入力と数式の作成を行います。</t>
         </is>
